--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.14784066637969</v>
+        <v>2.9490241082867</v>
       </c>
       <c r="D2" t="n">
-        <v>19.85676006789539</v>
+        <v>3.226723511033001</v>
       </c>
       <c r="E2" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F2" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.06479608718685</v>
+        <v>2.448029364167863</v>
       </c>
       <c r="D3" t="n">
-        <v>13.96029965329104</v>
+        <v>2.268548693659794</v>
       </c>
       <c r="E3" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F3" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.57825535183687</v>
+        <v>3.993966494673491</v>
       </c>
       <c r="D4" t="n">
-        <v>26.36489966263088</v>
+        <v>4.284296195177519</v>
       </c>
       <c r="E4" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F4" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.98944877445853</v>
+        <v>5.198285425849512</v>
       </c>
       <c r="D5" t="n">
-        <v>33.70110602323426</v>
+        <v>5.476429728775567</v>
       </c>
       <c r="E5" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F5" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.43708996517877</v>
+        <v>9.33352711934155</v>
       </c>
       <c r="D6" t="n">
-        <v>57.76972015081343</v>
+        <v>9.387579524507181</v>
       </c>
       <c r="E6" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F6" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.68981364200219</v>
+        <v>4.499594716825356</v>
       </c>
       <c r="D7" t="n">
-        <v>28.78980892126254</v>
+        <v>4.678343949705163</v>
       </c>
       <c r="E7" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F7" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.262872305702737</v>
+        <v>1.180216749676695</v>
       </c>
       <c r="D8" t="n">
-        <v>20.33478786841115</v>
+        <v>3.304403028616812</v>
       </c>
       <c r="E8" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F8" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.98254151058174</v>
+        <v>5.359662995469533</v>
       </c>
       <c r="D9" t="n">
-        <v>30.53734999421987</v>
+        <v>4.962319374060729</v>
       </c>
       <c r="E9" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F9" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>80.74544359728442</v>
+        <v>13.12113458455872</v>
       </c>
       <c r="D10" t="n">
-        <v>12.40649211355076</v>
+        <v>2.016054968451998</v>
       </c>
       <c r="E10" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F10" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>40.05293206432819</v>
+        <v>6.508601460453331</v>
       </c>
       <c r="D11" t="n">
-        <v>21.0059515376</v>
+        <v>3.413467124860001</v>
       </c>
       <c r="E11" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F11" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>76.93409077640095</v>
+        <v>12.50178975116516</v>
       </c>
       <c r="D12" t="n">
-        <v>11.24374488043364</v>
+        <v>1.827108543070467</v>
       </c>
       <c r="E12" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F12" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.58543624457956</v>
+        <v>5.295133389744179</v>
       </c>
       <c r="D13" t="n">
-        <v>11.01135777277262</v>
+        <v>1.789345638075551</v>
       </c>
       <c r="E13" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F13" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.61995595515564</v>
+        <v>2.700742842712792</v>
       </c>
       <c r="D14" t="n">
-        <v>6.18465843842649</v>
+        <v>1.005006996244305</v>
       </c>
       <c r="E14" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F14" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.01879369420981</v>
+        <v>3.578053975309095</v>
       </c>
       <c r="D15" t="n">
-        <v>16.97214797407311</v>
+        <v>2.757974045786881</v>
       </c>
       <c r="E15" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F15" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>25.52767114570107</v>
+        <v>4.148246561176424</v>
       </c>
       <c r="D16" t="n">
-        <v>20.11218536111877</v>
+        <v>3.2682301211818</v>
       </c>
       <c r="E16" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F16" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>11.47731252277557</v>
+        <v>1.86506328495103</v>
       </c>
       <c r="D17" t="n">
-        <v>8.01443879216051</v>
+        <v>1.302346303726083</v>
       </c>
       <c r="E17" t="n">
-        <v>21.01593635785247</v>
+        <v>3.415089658151027</v>
       </c>
       <c r="F17" t="n">
-        <v>12.29501329116874</v>
+        <v>1.997939659814921</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
